--- a/AC_2014/3-Karimnagar_9_28_Vemulawada.xlsx
+++ b/AC_2014/3-Karimnagar_9_28_Vemulawada.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,6 +50,11 @@
       <name val="Calibri"/>
       <b val="1"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="6">
@@ -84,7 +89,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -106,11 +111,33 @@
         <color rgb="00D3D3D3"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="double">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -145,6 +172,15 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -6574,7 +6610,7 @@
         </is>
       </c>
       <c r="C108" s="6" t="n">
-        <v>4017</v>
+        <v>0</v>
       </c>
       <c r="D108" s="6" t="n">
         <v>0</v>
@@ -6604,7 +6640,7 @@
         <v>0</v>
       </c>
       <c r="M108" s="6" t="n">
-        <v>4227</v>
+        <v>210</v>
       </c>
       <c r="N108" s="6" t="n">
         <v>0</v>
@@ -6613,7 +6649,7 @@
         <v>2</v>
       </c>
       <c r="P108" s="6" t="n">
-        <v>4229</v>
+        <v>212</v>
       </c>
       <c r="Q108" s="6" t="n">
         <v>0</v>
@@ -7450,7 +7486,7 @@
         <v>22</v>
       </c>
       <c r="E123" s="6" t="n">
-        <v>1648</v>
+        <v>0</v>
       </c>
       <c r="F123" s="6" t="n">
         <v>292</v>
@@ -7474,7 +7510,7 @@
         <v>24</v>
       </c>
       <c r="M123" s="6" t="n">
-        <v>2262</v>
+        <v>614</v>
       </c>
       <c r="N123" s="6" t="n">
         <v>0</v>
@@ -7483,7 +7519,7 @@
         <v>1</v>
       </c>
       <c r="P123" s="6" t="n">
-        <v>2263</v>
+        <v>615</v>
       </c>
       <c r="Q123" s="6" t="n">
         <v>0</v>
@@ -13583,202 +13619,203 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="7" t="inlineStr">
+      <c r="A229" s="18" t="inlineStr">
         <is>
           <t>TOTAL EVM VOTES</t>
         </is>
       </c>
-      <c r="B229" s="8" t="inlineStr"/>
-      <c r="C229" s="9">
+      <c r="B229" s="11" t="inlineStr"/>
+      <c r="C229" s="19">
         <f>SUM(C6:C228)</f>
         <v/>
       </c>
-      <c r="D229" s="9">
+      <c r="D229" s="19">
         <f>SUM(D6:D228)</f>
         <v/>
       </c>
-      <c r="E229" s="9">
+      <c r="E229" s="19">
         <f>SUM(E6:E228)</f>
         <v/>
       </c>
-      <c r="F229" s="9">
+      <c r="F229" s="19">
         <f>SUM(F6:F228)</f>
         <v/>
       </c>
-      <c r="G229" s="9">
+      <c r="G229" s="19">
         <f>SUM(G6:G228)</f>
         <v/>
       </c>
-      <c r="H229" s="9">
+      <c r="H229" s="19">
         <f>SUM(H6:H228)</f>
         <v/>
       </c>
-      <c r="I229" s="9">
+      <c r="I229" s="19">
         <f>SUM(I6:I228)</f>
         <v/>
       </c>
-      <c r="J229" s="9">
+      <c r="J229" s="19">
         <f>SUM(J6:J228)</f>
         <v/>
       </c>
-      <c r="K229" s="9">
+      <c r="K229" s="19">
         <f>SUM(K6:K228)</f>
         <v/>
       </c>
-      <c r="L229" s="9">
+      <c r="L229" s="19">
         <f>SUM(L6:L228)</f>
         <v/>
       </c>
-      <c r="M229" s="9">
+      <c r="M229" s="19">
         <f>SUM(M6:M228)</f>
         <v/>
       </c>
-      <c r="N229" s="9">
+      <c r="N229" s="19">
         <f>SUM(N6:N228)</f>
         <v/>
       </c>
-      <c r="O229" s="9">
+      <c r="O229" s="19">
         <f>SUM(O6:O228)</f>
         <v/>
       </c>
-      <c r="P229" s="9">
+      <c r="P229" s="19">
         <f>SUM(P6:P228)</f>
         <v/>
       </c>
-      <c r="Q229" s="9">
+      <c r="Q229" s="19">
         <f>SUM(Q6:Q228)</f>
         <v/>
       </c>
-      <c r="R229" s="9">
+      <c r="R229" s="19">
         <f>SUM(R6:R228)</f>
         <v/>
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="10" t="inlineStr">
+      <c r="A230" s="18" t="inlineStr">
         <is>
           <t>POSTAL BALLOT VOTES</t>
         </is>
       </c>
       <c r="B230" s="11" t="inlineStr"/>
-      <c r="C230" s="12" t="n">
+      <c r="C230" s="19" t="n">
         <v>186</v>
       </c>
-      <c r="D230" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="E230" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="F230" s="12" t="n">
+      <c r="D230" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E230" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="F230" s="19" t="n">
         <v>164</v>
       </c>
-      <c r="G230" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="H230" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I230" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J230" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K230" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L230" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M230" s="12" t="n">
+      <c r="G230" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H230" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I230" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J230" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K230" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L230" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M230" s="19" t="n">
         <v>361</v>
       </c>
-      <c r="N230" s="12" t="n">
+      <c r="N230" s="19" t="n">
         <v>88</v>
       </c>
-      <c r="O230" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="P230" s="12" t="n">
+      <c r="O230" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="P230" s="19" t="n">
         <v>451</v>
       </c>
-      <c r="Q230" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R230" s="13" t="n">
+      <c r="Q230" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R230" s="19" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="14" t="inlineStr">
+      <c r="A231" s="18" t="inlineStr">
         <is>
           <t>TOTAL VOTES POLLED</t>
         </is>
       </c>
-      <c r="B231" s="15" t="inlineStr"/>
-      <c r="C231" s="16">
+      <c r="B231" s="11" t="inlineStr"/>
+      <c r="C231" s="20">
         <f>C229+C230</f>
         <v/>
       </c>
-      <c r="D231" s="16">
+      <c r="D231" s="20">
         <f>D229+D230</f>
         <v/>
       </c>
-      <c r="E231" s="16">
+      <c r="E231" s="20">
         <f>E229+E230</f>
         <v/>
       </c>
-      <c r="F231" s="16">
+      <c r="F231" s="20">
         <f>F229+F230</f>
         <v/>
       </c>
-      <c r="G231" s="16">
+      <c r="G231" s="20">
         <f>G229+G230</f>
         <v/>
       </c>
-      <c r="H231" s="16">
+      <c r="H231" s="20">
         <f>H229+H230</f>
         <v/>
       </c>
-      <c r="I231" s="16">
+      <c r="I231" s="20">
         <f>I229+I230</f>
         <v/>
       </c>
-      <c r="J231" s="16">
+      <c r="J231" s="20">
         <f>J229+J230</f>
         <v/>
       </c>
-      <c r="K231" s="16">
+      <c r="K231" s="20">
         <f>K229+K230</f>
         <v/>
       </c>
-      <c r="L231" s="16">
+      <c r="L231" s="20">
         <f>L229+L230</f>
         <v/>
       </c>
-      <c r="M231" s="16">
+      <c r="M231" s="20">
         <f>M229+M230</f>
         <v/>
       </c>
-      <c r="N231" s="16">
+      <c r="N231" s="20">
         <f>N229+N230</f>
         <v/>
       </c>
-      <c r="O231" s="16">
+      <c r="O231" s="20">
         <f>O229+O230</f>
         <v/>
       </c>
-      <c r="P231" s="16">
+      <c r="P231" s="20">
         <f>P229+P230</f>
         <v/>
       </c>
-      <c r="Q231" s="16">
+      <c r="Q231" s="20">
         <f>Q229+Q230</f>
         <v/>
       </c>
-      <c r="R231" s="17" t="n">
-        <v>0</v>
+      <c r="R231" s="20">
+        <f>R229+R230</f>
+        <v/>
       </c>
     </row>
   </sheetData>
